--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_valparaiso.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_valparaiso.xlsx
@@ -397,7 +397,7 @@
         <v>61.29610292930857</v>
       </c>
       <c r="E2">
-        <v>23.98356978394991</v>
+        <v>23.9835697839499</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         <v>16.01247957212896</v>
       </c>
       <c r="D3">
-        <v>62.39488931808052</v>
+        <v>62.39488931808053</v>
       </c>
       <c r="E3">
         <v>21.59263110979052</v>
@@ -486,7 +486,7 @@
         <v>134.4170573113564</v>
       </c>
       <c r="C7">
-        <v>17.48730696001692</v>
+        <v>17.48730696001693</v>
       </c>
       <c r="D7">
         <v>59.00676962132431</v>
@@ -511,7 +511,7 @@
         <v>60.88422565077084</v>
       </c>
       <c r="E8">
-        <v>25.03114082605748</v>
+        <v>25.03114082605749</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         <v>61.32245857462301</v>
       </c>
       <c r="E10">
-        <v>22.42560632991228</v>
+        <v>22.42560632991227</v>
       </c>
     </row>
     <row r="11">
@@ -603,7 +603,7 @@
         <v>16.77805299808384</v>
       </c>
       <c r="D13">
-        <v>61.48058138991448</v>
+        <v>61.48058138991447</v>
       </c>
       <c r="E13">
         <v>21.74136561200168</v>
@@ -714,10 +714,10 @@
         <v>145.8364497631513</v>
       </c>
       <c r="C19">
-        <v>15.65619602447378</v>
+        <v>15.65619602447379</v>
       </c>
       <c r="D19">
-        <v>61.51136352547401</v>
+        <v>61.51136352547402</v>
       </c>
       <c r="E19">
         <v>22.83244045005221</v>
@@ -739,7 +739,7 @@
         <v>63.37533567444743</v>
       </c>
       <c r="E20">
-        <v>19.6240446188804</v>
+        <v>19.62404461888039</v>
       </c>
     </row>
     <row r="21">
@@ -771,13 +771,13 @@
         <v>107.8427378284783</v>
       </c>
       <c r="C22">
-        <v>18.19158791921438</v>
+        <v>18.19158791921437</v>
       </c>
       <c r="D22">
-        <v>62.19010561423013</v>
+        <v>62.19010561423012</v>
       </c>
       <c r="E22">
-        <v>19.6183064665555</v>
+        <v>19.61830646655549</v>
       </c>
     </row>
     <row r="23">
@@ -812,10 +812,10 @@
         <v>16.60190129175428</v>
       </c>
       <c r="D24">
-        <v>61.20764005310438</v>
+        <v>61.20764005310437</v>
       </c>
       <c r="E24">
-        <v>22.19045865514134</v>
+        <v>22.19045865514133</v>
       </c>
     </row>
     <row r="25">
@@ -831,10 +831,10 @@
         <v>14.15380374862183</v>
       </c>
       <c r="D25">
-        <v>55.22785740536568</v>
+        <v>55.22785740536567</v>
       </c>
       <c r="E25">
-        <v>30.6183388460125</v>
+        <v>30.61833884601249</v>
       </c>
     </row>
     <row r="26">
@@ -850,10 +850,10 @@
         <v>16.87528975428836</v>
       </c>
       <c r="D26">
-        <v>57.00224671017439</v>
+        <v>57.00224671017438</v>
       </c>
       <c r="E26">
-        <v>26.12246353553725</v>
+        <v>26.12246353553724</v>
       </c>
     </row>
     <row r="27">
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>205.2352941176471</v>
+        <v>205.235294117647</v>
       </c>
       <c r="C27">
         <v>14.87639466199956</v>
       </c>
       <c r="D27">
-        <v>54.59199299934369</v>
+        <v>54.5919929993437</v>
       </c>
       <c r="E27">
         <v>30.53161233865675</v>
@@ -910,7 +910,7 @@
         <v>61.22900352680973</v>
       </c>
       <c r="E29">
-        <v>24.02414968019607</v>
+        <v>24.02414968019606</v>
       </c>
     </row>
     <row r="30">
@@ -926,7 +926,7 @@
         <v>17.39215255931914</v>
       </c>
       <c r="D30">
-        <v>61.73214329260858</v>
+        <v>61.73214329260857</v>
       </c>
       <c r="E30">
         <v>20.87570414807228</v>
@@ -964,7 +964,7 @@
         <v>20.63885997918501</v>
       </c>
       <c r="D32">
-        <v>65.80738131454648</v>
+        <v>65.80738131454646</v>
       </c>
       <c r="E32">
         <v>13.55375870626851</v>
@@ -986,7 +986,7 @@
         <v>67.52876295521537</v>
       </c>
       <c r="E33">
-        <v>19.1214224588761</v>
+        <v>19.12142245887611</v>
       </c>
     </row>
     <row r="34">
@@ -1024,7 +1024,7 @@
         <v>60.61356362099161</v>
       </c>
       <c r="E35">
-        <v>22.73084123437406</v>
+        <v>22.73084123437405</v>
       </c>
     </row>
     <row r="36">
@@ -1081,7 +1081,7 @@
         <v>57.85257148119158</v>
       </c>
       <c r="E38">
-        <v>26.33178323127216</v>
+        <v>26.33178323127215</v>
       </c>
     </row>
     <row r="39">
